--- a/ejemplo_gastos_validos.xlsx
+++ b/ejemplo_gastos_validos.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -523,7 +523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MXN</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="E4" t="n">
